--- a/cashier/不合规明细.xlsx
+++ b/cashier/不合规明细.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不合规明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="不合规明细" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/cashier/不合规明细.xlsx
+++ b/cashier/不合规明细.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5881,37 +5881,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>华为北京上德银泰</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>华为北京上德银泰</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>LSD2026080100897355</t>
+          <t>LSD2026080500921272</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5920,58 +5920,58 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>66</v>
+        <v>21598</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>+86-139****2518</t>
+          <t>181****9239</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>2084600368103059462</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>LSD2026080100896430</t>
+          <t>LSD2026080500921203</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5980,58 +5980,58 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>14500</v>
+        <v>1378</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>+86-186****1534</t>
+          <t>+86-186****4657</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>2084894536964186120</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>LSD2026080100901135</t>
+          <t>LSD2026080500919261</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6040,58 +6040,58 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>13799</v>
+        <v>11299</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>+86-158****6261</t>
+          <t>+86-137****9681</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>2084829482505408520</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>APR北京怀柔万达</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>APR北京怀柔万达</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>LSD2026080100896731</t>
+          <t>LSD2026080500920152</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6100,58 +6100,58 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>199</v>
+        <v>798</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>+86-186****9666</t>
+          <t>135****4525</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>2084871296859967489</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>APR北京龙德广场</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>APR北京龙德广场</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LSD2026080100900020</t>
+          <t>LSD2026080500920389</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6160,58 +6160,58 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>100</v>
+        <v>649</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>+86-138****2964</t>
+          <t>+86-151****4504</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>2084883374583341065</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>APR北京龙德广场</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>APR北京龙德广场</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>LSD2026080100899803</t>
+          <t>LSD2026080500919681</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6220,21 +6220,21 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>200</v>
+        <v>498</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>+86-137****5245</t>
+          <t>+86-150****7892</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>2084852832236150789</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>华为北京上德银泰</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>华为北京上德银泰</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>LSD2026080100896058</t>
+          <t>LSD2026080100897355</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6280,11 +6280,11 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>11999</v>
+        <v>66</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>+86-133****6607</t>
+          <t>+86-139****2518</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6316,22 +6316,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LSD2026080100896643</t>
+          <t>LSD2026080100896430</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6340,11 +6340,11 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4479</v>
+        <v>14500</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>+86-158****9578</t>
+          <t>+86-186****1534</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LSD2026080100894796</t>
+          <t>LSD2026080100901135</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6400,11 +6400,11 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>199</v>
+        <v>13799</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-158****6261</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京大兴大族</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京大兴大族</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LSD2026080100900639</t>
+          <t>LSD2026080100896731</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6460,11 +6460,11 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>10499</v>
+        <v>199</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>+86-190****1802</t>
+          <t>+86-186****9666</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>LSD2026080100896928</t>
+          <t>LSD2026080100900020</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6520,11 +6520,11 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>19999</v>
+        <v>100</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>+86-156****1888</t>
+          <t>+86-138****2964</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LSD2026080100896290</t>
+          <t>LSD2026080100899803</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6580,11 +6580,11 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>579</v>
+        <v>200</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>+86-136****0769</t>
+          <t>+86-137****5245</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LSD2026080100900497</t>
+          <t>LSD2026080100896058</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6640,11 +6640,11 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>15496</v>
+        <v>11999</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-133****6607</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6676,22 +6676,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LSD2026080100895696</t>
+          <t>LSD2026080100896643</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6700,11 +6700,11 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>12999</v>
+        <v>4479</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-158****9578</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LSD2026080100895833</t>
+          <t>LSD2026080100894796</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6760,11 +6760,11 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>11499</v>
+        <v>199</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>+86-186****7992</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6796,22 +6796,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>LSD2026080100900636</t>
+          <t>LSD2026080100900639</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6820,21 +6820,21 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>8508</v>
+        <v>10499</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>135****5178</t>
+          <t>+86-190****1802</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>260801000210361243</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LSD2026080100900521</t>
+          <t>LSD2026080100896928</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6880,21 +6880,21 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8508</v>
+        <v>19999</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>135****5178</t>
+          <t>+86-156****1888</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>260801000210359210</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6916,12 +6916,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LSD2026080100895081</t>
+          <t>LSD2026080100896290</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6940,11 +6940,11 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7499</v>
+        <v>579</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>158****6735</t>
+          <t>+86-136****0769</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>LSD2026080100902100</t>
+          <t>LSD2026080100900497</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7000,11 +7000,11 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>15496</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>185****8918</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>LSD2026080100901934</t>
+          <t>LSD2026080100895696</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7060,11 +7060,11 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>11500</v>
+        <v>12999</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>185****8918</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LSD2026080100901580</t>
+          <t>LSD2026080100895833</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7120,11 +7120,11 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>100</v>
+        <v>11499</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>+86-139****8563</t>
+          <t>+86-186****7992</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7156,22 +7156,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LSD2026080100899751</t>
+          <t>LSD2026080100900636</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7180,21 +7180,21 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1199</v>
+        <v>8508</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>+86-186****3681</t>
+          <t>135****5178</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>260801000210361243</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>LSD2026080100898752</t>
+          <t>LSD2026080100900521</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7240,21 +7240,21 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>11999</v>
+        <v>8508</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>+86-132****5290</t>
+          <t>135****5178</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>260801000210359210</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>LSD2026080100896152</t>
+          <t>LSD2026080100895081</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7300,11 +7300,11 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>14999</v>
+        <v>7499</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>+86-189****0781</t>
+          <t>158****6735</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LSD2026080100896120</t>
+          <t>LSD2026080100902100</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7360,11 +7360,11 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>12999</v>
+        <v>3</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>+86-137****4764</t>
+          <t>185****8918</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7374,19 +7374,19 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LSD2026080200906084</t>
+          <t>LSD2026080100901934</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7420,11 +7420,11 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1319</v>
+        <v>11500</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>+86-173****8086</t>
+          <t>185****8918</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7434,19 +7434,19 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LSD2026080200902575</t>
+          <t>LSD2026080100901580</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7480,11 +7480,11 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>+86-133****8655</t>
+          <t>+86-139****8563</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7494,19 +7494,19 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7516,22 +7516,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LSD2026080200907628</t>
+          <t>LSD2026080100899751</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7540,11 +7540,11 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>200</v>
+        <v>1199</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>+86-133****3358</t>
+          <t>+86-186****3681</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7554,19 +7554,19 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LSD2026080200906688</t>
+          <t>LSD2026080100898752</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7600,11 +7600,11 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>199</v>
+        <v>11999</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>+86-137****3871</t>
+          <t>+86-132****5290</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7614,19 +7614,19 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LSD2026080200904013</t>
+          <t>LSD2026080100896152</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7660,11 +7660,11 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1199</v>
+        <v>14999</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>+86-135****2380</t>
+          <t>+86-189****0781</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7674,19 +7674,19 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LSD2026080200903906</t>
+          <t>LSD2026080100896120</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7720,11 +7720,11 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>69</v>
+        <v>12999</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>+86-187****1204</t>
+          <t>+86-137****4764</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LSD2026080200902846</t>
+          <t>LSD2026080200906084</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7780,11 +7780,11 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>13999</v>
+        <v>1319</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>+86-158****7802</t>
+          <t>+86-173****8086</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LSD2026080200903265</t>
+          <t>LSD2026080200902575</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7840,11 +7840,11 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1249</v>
+        <v>200</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>+86-137****5188</t>
+          <t>+86-133****8655</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7876,22 +7876,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LSD2026080200904032</t>
+          <t>LSD2026080200907628</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7900,11 +7900,11 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4498</v>
+        <v>200</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>+86-156****9614</t>
+          <t>+86-133****3358</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LSD2026080200902738</t>
+          <t>LSD2026080200906688</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7960,11 +7960,11 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>9196</v>
+        <v>199</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-137****3871</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>LSD2026080200902568</t>
+          <t>LSD2026080200904013</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8020,11 +8020,11 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6999</v>
+        <v>1199</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-135****2380</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>LSD2026080200902559</t>
+          <t>LSD2026080200903906</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8080,11 +8080,11 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>16497</v>
+        <v>69</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-187****1204</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8116,12 +8116,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LSD2026080200906772</t>
+          <t>LSD2026080200902846</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8140,11 +8140,11 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>12699</v>
+        <v>13999</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>+86-139****3939</t>
+          <t>+86-158****7802</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LSD2026080200905752</t>
+          <t>LSD2026080200903265</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8200,11 +8200,11 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>12500</v>
+        <v>1249</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>+86-132****9058</t>
+          <t>+86-137****5188</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8236,12 +8236,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LSD2026080200902812</t>
+          <t>LSD2026080200904032</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8260,11 +8260,11 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>300</v>
+        <v>4498</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>+86-185****8357</t>
+          <t>+86-156****9614</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LSD2026080200907332</t>
+          <t>LSD2026080200902738</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8320,11 +8320,11 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>50</v>
+        <v>9196</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>+86-151****4775</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8334,19 +8334,19 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LSD2026080300909417</t>
+          <t>LSD2026080200902568</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8380,11 +8380,11 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>599</v>
+        <v>6999</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8394,19 +8394,19 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8416,22 +8416,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LSD2026080300909417</t>
+          <t>LSD2026080200902559</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8440,11 +8440,11 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>599</v>
+        <v>16497</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8454,19 +8454,19 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LSD2026080300909361</t>
+          <t>LSD2026080200906772</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8500,11 +8500,11 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>12599</v>
+        <v>12699</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>+86-139****3939</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8514,19 +8514,19 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8536,22 +8536,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LSD2026080300908984</t>
+          <t>LSD2026080200905752</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8560,11 +8560,11 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>199</v>
+        <v>12500</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>+86-132****9058</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8574,19 +8574,19 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>LSD2026080300912449</t>
+          <t>LSD2026080200902812</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8620,11 +8620,11 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>49</v>
+        <v>300</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>139****9854</t>
+          <t>+86-185****8357</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8634,19 +8634,19 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LSD2026080300909916</t>
+          <t>LSD2026080200907332</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8680,11 +8680,11 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>8299</v>
+        <v>50</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>+86-158****7802</t>
+          <t>+86-151****4775</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LSD2026080300912336</t>
+          <t>LSD2026080300909417</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8740,11 +8740,11 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>13800</v>
+        <v>599</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>+86-188****0892</t>
+          <t>+86-131****8359</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8776,22 +8776,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LSD2026080300908272</t>
+          <t>LSD2026080300909417</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8800,11 +8800,11 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>10</v>
+        <v>599</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>+86-136****3866</t>
+          <t>+86-131****8359</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>华为北京回龙观万科</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>华为北京回龙观万科</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>LSD2026080300909392</t>
+          <t>LSD2026080300909361</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8860,11 +8860,11 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5197</v>
+        <v>12599</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>+86-186****2999</t>
+          <t>+86-131****8359</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8896,22 +8896,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>LSD2026080300908982</t>
+          <t>LSD2026080300908984</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8920,11 +8920,11 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>+86-136****4596</t>
+          <t>+86-131****8359</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>LSD2026080300908672</t>
+          <t>LSD2026080300912449</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8980,11 +8980,11 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>+86-135****3541</t>
+          <t>139****9854</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>LSD2026080300913369</t>
+          <t>LSD2026080300909916</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9040,11 +9040,11 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>85</v>
+        <v>8299</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>+86-136****6230</t>
+          <t>+86-158****7802</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9076,12 +9076,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>LSD2026080300909492</t>
+          <t>LSD2026080300912336</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9100,11 +9100,11 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1000</v>
+        <v>13800</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>+86-135****7391</t>
+          <t>+86-188****0892</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>LSD2026080300909357</t>
+          <t>LSD2026080300908272</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9160,11 +9160,11 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6899</v>
+        <v>10</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>+86-187****9725</t>
+          <t>+86-136****3866</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京回龙观万科</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京回龙观万科</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>LSD2026080300909921</t>
+          <t>LSD2026080300909392</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9220,11 +9220,11 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>99</v>
+        <v>5197</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>+86-136****2871</t>
+          <t>+86-186****2999</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9256,22 +9256,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LSD2026080300911187</t>
+          <t>LSD2026080300908982</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>+86-136****4417</t>
+          <t>+86-136****4596</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9316,12 +9316,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>LSD2026080300908774</t>
+          <t>LSD2026080300908672</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9340,11 +9340,11 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>299</v>
+        <v>200</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>+86-139****6913</t>
+          <t>+86-135****3541</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>华为北京酒仙桥颐堤港</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>华为北京酒仙桥颐堤港</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LSD2026080300912154</t>
+          <t>LSD2026080300913369</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9400,11 +9400,11 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>+86-136****5348</t>
+          <t>+86-136****6230</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>LSD2026080300912804</t>
+          <t>LSD2026080300909492</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9460,11 +9460,11 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1149</v>
+        <v>1000</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>+86-135****7766</t>
+          <t>+86-135****7391</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9474,19 +9474,19 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LSD2026080400915041</t>
+          <t>LSD2026080300909357</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9520,11 +9520,11 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>6899</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>+86-178****1967</t>
+          <t>+86-187****9725</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9534,19 +9534,19 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>华为北京回龙观万科</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>华为北京回龙观万科</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>LSD2026080400916024</t>
+          <t>LSD2026080300909921</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9580,11 +9580,11 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.1</v>
+        <v>99</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>153****1994</t>
+          <t>+86-136****2871</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9594,19 +9594,19 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9616,22 +9616,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>LSD2026080400918034</t>
+          <t>LSD2026080300911187</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9640,11 +9640,11 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3799</v>
+        <v>99</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>+86-156****9614</t>
+          <t>+86-136****4417</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9654,19 +9654,19 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9676,22 +9676,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>LSD2026080400917521</t>
+          <t>LSD2026080300908774</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9700,11 +9700,11 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4597</v>
+        <v>299</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>+86-151****0897</t>
+          <t>+86-139****6913</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9714,19 +9714,19 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为北京酒仙桥颐堤港</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为北京酒仙桥颐堤港</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>LSD2026080400918760</t>
+          <t>LSD2026080300912154</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9760,11 +9760,11 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>+86-185****1770</t>
+          <t>+86-136****5348</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9774,19 +9774,19 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LSD2026080400917071</t>
+          <t>LSD2026080300912804</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9820,11 +9820,11 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>10299</v>
+        <v>1149</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>+86-187****8972</t>
+          <t>+86-135****7766</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>LSD2026080400918913</t>
+          <t>LSD2026080400915041</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -9880,11 +9880,11 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>498</v>
+        <v>1</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>+86-158****1870</t>
+          <t>+86-178****1967</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京回龙观万科</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9916,22 +9916,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京回龙观万科</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>LSD2026080400916776</t>
+          <t>LSD2026080400916024</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -9940,11 +9940,11 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>194</v>
+        <v>0.1</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>188****2372</t>
+          <t>153****1994</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>LSD2026080400918472</t>
+          <t>LSD2026080400918034</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10000,11 +10000,11 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>500</v>
+        <v>3799</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>133****0100</t>
+          <t>+86-156****9614</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京大兴大族</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10036,22 +10036,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京大兴大族</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>LSD2026080400918417</t>
+          <t>LSD2026080400917521</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10060,11 +10060,11 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.4</v>
+        <v>4597</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>133****0100</t>
+          <t>+86-151****0897</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10096,12 +10096,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>LSD2026080400918413</t>
+          <t>LSD2026080400918760</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>+86-198****6299</t>
+          <t>+86-185****1770</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10156,12 +10156,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>LSD2026080400918405</t>
+          <t>LSD2026080400917071</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10180,11 +10180,11 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>500</v>
+        <v>10299</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>+86-198****6299</t>
+          <t>+86-187****8972</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10194,44 +10194,44 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>LSD2026080100901829</t>
+          <t>LSD2026080400918913</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10240,11 +10240,11 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2999</v>
+        <v>498</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-158****1870</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10254,34 +10254,34 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>LSD2026080100899130</t>
+          <t>LSD2026080400916776</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10300,11 +10300,11 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4026</v>
+        <v>194</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>188****2372</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10321,37 +10321,37 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>LSD2026080100898610</t>
+          <t>LSD2026080400918472</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10360,11 +10360,11 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>599</v>
+        <v>500</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>133****0100</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10374,44 +10374,44 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>LSD2026080100896089</t>
+          <t>LSD2026080400918417</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10420,11 +10420,11 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3917</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>177****2965</t>
+          <t>133****0100</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10434,44 +10434,44 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>LSD2026080100901711</t>
+          <t>LSD2026080400918413</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10480,11 +10480,11 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1398</v>
+        <v>200</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>184****5224</t>
+          <t>+86-198****6299</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10494,44 +10494,44 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>LSD2026080100899296</t>
+          <t>LSD2026080400918405</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10540,11 +10540,11 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3697</v>
+        <v>500</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-198****6299</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10554,34 +10554,34 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>LSD2026080100896505</t>
+          <t>LSD2026080500920772</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10600,11 +10600,11 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5999</v>
+        <v>12799</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>+86-133****4816</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10621,37 +10621,37 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DJI北京昌平超级合生汇授权体验店</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>DJI北京昌平超级合生汇授权体验店</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>LSD2026080100897329</t>
+          <t>LSD2026080500919293</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10660,11 +10660,11 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2767</v>
+        <v>11699</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>137****2423</t>
+          <t>+86-132****0312</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10674,44 +10674,44 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DJI北京望京凯德MALL授权体验店</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DJI北京望京凯德MALL授权体验店</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>LSD2026080100897080</t>
+          <t>LSD2026080500919219</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>银联POS手动收款</t>
+          <t>刷卡扫码-银联</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10720,11 +10720,11 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3799</v>
+        <v>7299</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>139****5407</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>不合规（公司禁用收款通道）</t>
+          <t>不合规（缺三方单号）</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DJI北京王府井APM授权高级体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DJI北京王府井APM授权高级体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>LSD2026080100895818</t>
+          <t>LSD2026080100901829</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3218</v>
+        <v>2999</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DJI北京蓝色港湾授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>DJI北京蓝色港湾授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>LSD2026080100901804</t>
+          <t>LSD2026080100899130</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10840,11 +10840,11 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3355</v>
+        <v>4026</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DJI北京蓝色港湾授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DJI北京蓝色港湾授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>LSD2026080100901182</t>
+          <t>LSD2026080100898610</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10900,11 +10900,11 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2298</v>
+        <v>599</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DJI北京顺义华联授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10936,12 +10936,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DJI北京顺义华联授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>LSD2026080100899548</t>
+          <t>LSD2026080100896089</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10960,11 +10960,11 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5499</v>
+        <v>3917</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>158****9456</t>
+          <t>177****2965</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DJI北京龙德广场授权体验店</t>
+          <t>DJI北京丰科万达广场授权体验店</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>DJI北京龙德广场授权体验店</t>
+          <t>DJI北京丰科万达广场授权体验店</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>LSD2026080100900940</t>
+          <t>LSD2026080100901711</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11020,11 +11020,11 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>558</v>
+        <v>1398</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>+86-183****7721</t>
+          <t>184****5224</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11041,12 +11041,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>LSD2026080200906536</t>
+          <t>LSD2026080100899296</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1698</v>
+        <v>3697</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -11101,12 +11101,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>LSD2026080200906207</t>
+          <t>LSD2026080100896505</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4174</v>
+        <v>5999</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -11161,12 +11161,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京昌平超级合生汇授权体验店</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11176,12 +11176,12 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京昌平超级合生汇授权体验店</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>LSD2026080200905999</t>
+          <t>LSD2026080100897329</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11200,11 +11200,11 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3799</v>
+        <v>2767</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>137****2423</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11221,12 +11221,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京望京凯德MALL授权体验店</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京望京凯德MALL授权体验店</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>LSD2026080200905881</t>
+          <t>LSD2026080100897080</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11281,12 +11281,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DJI北京中关村大融城授权体验店</t>
+          <t>DJI北京王府井APM授权高级体验店</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11296,12 +11296,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DJI北京中关村大融城授权体验店</t>
+          <t>DJI北京王府井APM授权高级体验店</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>LSD2026080200902869</t>
+          <t>LSD2026080100895818</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -11320,11 +11320,11 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3898</v>
+        <v>3218</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>172****4364</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11341,12 +11341,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI北京蓝色港湾授权体验店</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11356,12 +11356,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI北京蓝色港湾授权体验店</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>LSD2026080200907365</t>
+          <t>LSD2026080100901804</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -11380,11 +11380,11 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>5244</v>
+        <v>3355</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>138****7017</t>
+          <t>135****5980</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11401,7 +11401,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>LSD2026080200907986</t>
+          <t>LSD2026080100901182</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5845</v>
+        <v>2298</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -11461,12 +11461,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DJI北京西单大悦城授权体验店</t>
+          <t>DJI北京顺义华联授权体验店</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>DJI北京西单大悦城授权体验店</t>
+          <t>DJI北京顺义华联授权体验店</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>LSD2026080200904058</t>
+          <t>LSD2026080100899548</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -11500,11 +11500,11 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>699</v>
+        <v>5499</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>158****9456</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11521,12 +11521,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京龙德广场授权体验店</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI北京龙德广场授权体验店</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>LSD2026080300910015</t>
+          <t>LSD2026080100900940</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11560,11 +11560,11 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4299</v>
+        <v>558</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>138****1500</t>
+          <t>+86-183****7721</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11581,12 +11581,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11596,12 +11596,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>LSD2026080300908669</t>
+          <t>LSD2026080200906536</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -11620,11 +11620,11 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3108</v>
+        <v>1698</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>157****2651</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11641,12 +11641,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>LSD2026080300911774</t>
+          <t>LSD2026080200906207</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -11680,11 +11680,11 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3799</v>
+        <v>4174</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>134****2963</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11701,12 +11701,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11716,12 +11716,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>LSD2026080300910197</t>
+          <t>LSD2026080200905999</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -11740,11 +11740,11 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>23655</v>
+        <v>3799</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>186****1441</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11761,12 +11761,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>LSD2026080400914812</t>
+          <t>LSD2026080200905881</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>186****9390</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11821,12 +11821,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DJI北京龙德广场授权体验店</t>
+          <t>DJI北京中关村大融城授权体验店</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DJI北京龙德广场授权体验店</t>
+          <t>DJI北京中关村大融城授权体验店</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>LSD2026080400916197</t>
+          <t>LSD2026080200902869</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -11860,11 +11860,11 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4334</v>
+        <v>3898</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>152****3830</t>
+          <t>172****4364</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11881,37 +11881,37 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>APR成都温江旭辉</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>APR成都温江旭辉</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>LSD2026080100899328</t>
+          <t>LSD2026080200907365</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -11920,11 +11920,11 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>198</v>
+        <v>5244</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>+86-181****3714</t>
+          <t>138****7017</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11934,44 +11934,44 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京蓝色港湾授权体验店</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京蓝色港湾授权体验店</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>LSD2026080100899002</t>
+          <t>LSD2026080200907986</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -11980,11 +11980,11 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>280</v>
+        <v>5845</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>+86-134****6425</t>
+          <t>135****5980</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -12006,32 +12006,32 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>APR成都温江旭辉</t>
+          <t>DJI北京西单大悦城授权体验店</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>APR成都温江旭辉</t>
+          <t>DJI北京西单大悦城授权体验店</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>LSD2026080200905320</t>
+          <t>LSD2026080200904058</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12040,11 +12040,11 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>198</v>
+        <v>699</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>+86-186****1921</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -12054,44 +12054,44 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>LSD2026080200907760</t>
+          <t>LSD2026080300910015</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12100,11 +12100,11 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>100</v>
+        <v>4299</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>+86-159****4633</t>
+          <t>138****1500</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
@@ -12126,32 +12126,32 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>LSD2026080300909943</t>
+          <t>LSD2026080300908669</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12160,11 +12160,11 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2699</v>
+        <v>3108</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>+86-136****8289</t>
+          <t>157****2651</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -12174,44 +12174,44 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>LSD2026080400917692</t>
+          <t>LSD2026080300911774</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>刷卡扫码-银联</t>
+          <t>银联POS手动收款</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12220,11 +12220,11 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>178</v>
+        <v>3799</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>139****7878</t>
+          <t>134****2963</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -12234,34 +12234,34 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>不合规（刷卡扫码-银联，缺三方单号）</t>
+          <t>不合规（公司禁用收款通道）</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>华为福州平潭吾悦</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>华为福州平潭吾悦</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>LSD2026080100897932</t>
+          <t>LSD2026080300910197</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12280,11 +12280,11 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>79</v>
+        <v>23655</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>+86-178****0594</t>
+          <t>186****1441</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -12301,27 +12301,27 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>华为厦门思明瑞景广场</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>华为厦门思明瑞景广场</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>LSD2026080300912465</t>
+          <t>LSD2026080400914812</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -12340,11 +12340,11 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>7499</v>
+        <v>3799</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>+86-189****0178</t>
+          <t>186****9390</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -12361,12 +12361,792 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>DJI北京龙德广场授权体验店</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DJI北京龙德广场授权体验店</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>LSD2026080400916197</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>4334</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>152****3830</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>不合规（公司禁用收款通道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>DJI北京东方新天地授权体验店</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DJI北京东方新天地授权体验店</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>LSD2026080500919742</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>1299</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>不合规（公司禁用收款通道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>DJI北京京西大悦城授权体验店</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DJI北京京西大悦城授权体验店</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>LSD2026080500918990</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>3646</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>173****2982</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>不合规（公司禁用收款通道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>DJI北京金源购物广场授权体验店</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DJI北京金源购物广场授权体验店</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>LSD2026080500921307</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>5999</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>135****2633</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>不合规（公司禁用收款通道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>APR成都温江旭辉</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>APR成都温江旭辉</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>LSD2026080100899328</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>198</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>+86-181****3714</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>不合规（缺三方单号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>LSD2026080100899002</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>280</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>+86-134****6425</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>不合规（缺三方单号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>APR成都温江旭辉</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>APR成都温江旭辉</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>LSD2026080200905320</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>198</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>+86-186****1921</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>不合规（缺三方单号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>LSD2026080200907760</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>100</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>+86-159****4633</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>不合规（缺三方单号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>LSD2026080300909943</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>2699</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>+86-136****8289</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>不合规（缺三方单号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>LSD2026080400917692</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>178</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>139****7878</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>不合规（缺三方单号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>APR成都科华王府井</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>LSD2026080500920090</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>刷卡扫码-银联</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>280</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>159****9395</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>不合规（缺三方单号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>华为福州平潭吾悦</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>华为福州平潭吾悦</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>LSD2026080100897932</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>79</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>+86-178****0594</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>不合规（公司禁用收款通道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>华为厦门思明瑞景广场</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>华为厦门思明瑞景广场</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>LSD2026080300912465</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>银联POS手动收款</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>7499</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>+86-189****0178</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>不合规（公司禁用收款通道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>198 笔</t>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>211 笔</t>
         </is>
       </c>
     </row>

--- a/cashier/不合规明细.xlsx
+++ b/cashier/不合规明细.xlsx
@@ -415,6 +415,9 @@
   </sheetPr>
   <dimension ref="A1:L241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/cashier/不合规明细.xlsx
+++ b/cashier/不合规明细.xlsx
@@ -413,11 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L241"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -462,20 +459,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>实收金额</t>
+          <t>会员手机号</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>会员手机号</t>
+          <t>第三方订单号</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>第三方订单号</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -522,20 +514,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>2874</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>150****6552</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>150****6552</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -582,20 +571,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>3808</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>177****0229</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>177****0229</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -642,20 +628,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>7781.6</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>158****7998</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>158****7998</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -702,20 +685,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>2297</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>135****5494</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -762,20 +742,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>2397</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>135****5494</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -822,20 +799,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>3650.52</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>186****9677</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>186****9677</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -882,20 +856,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>23988</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -942,20 +913,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>2598</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1002,20 +970,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1155</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>188****7855</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1062,20 +1027,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1155</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>188****7855</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1122,20 +1084,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>1647</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>188****7855</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1182,20 +1141,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>5087</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>137****9080</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>137****9080</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1242,20 +1198,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>24</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1302,20 +1255,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>289</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>138****4526</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>138****4526</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1362,20 +1312,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>199</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>138****5533</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>138****5533</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1422,20 +1369,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>2499</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1482,20 +1426,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>3988</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1542,20 +1483,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>15693</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>185****5918</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>185****5918</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1602,20 +1540,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>32084</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>185****5918</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>185****5918</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1662,20 +1597,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>4687</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>188****3772</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>188****3772</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1722,20 +1654,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>4547</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>183****5937</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>183****5937</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1782,20 +1711,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>599</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1842,20 +1768,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>349</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>189****1806</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>189****1806</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1902,20 +1825,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>3799</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>139****1884</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>139****1884</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1962,20 +1882,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>249</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+86-150****9917</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>+86-150****9917</t>
+          <t>2083435200665018369</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
-        <is>
-          <t>2083435200665018369</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2022,20 +1939,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>598</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+86-135****9969</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>+86-135****9969</t>
+          <t>2083485389348970505</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
-        <is>
-          <t>2083485389348970505</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2082,20 +1996,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>10198.1</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>+86-139****7048</t>
+        </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>+86-139****7048</t>
+          <t>2083476392870047750</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
-        <is>
-          <t>2083476392870047750</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2142,20 +2053,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>6499</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+86-155****0158</t>
+        </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>+86-155****0158</t>
+          <t>2083434705134288904</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
-        <is>
-          <t>2083434705134288904</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2202,20 +2110,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>11499</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>+86-134****7207</t>
+        </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>+86-134****7207</t>
+          <t>2083399273130491907</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
-        <is>
-          <t>2083399273130491907</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2262,20 +2167,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>1849</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>2083530245690810368</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
-        <is>
-          <t>2083530245690810368</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2322,20 +2224,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>1298</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>+86-152****2966</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>+86-152****2966</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2382,20 +2281,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>1099</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>+86-150****7583</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>+86-150****7583</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2442,20 +2338,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>1099</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+86-132****8817</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>+86-132****8817</t>
+          <t>20834194****6625799</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
-        <is>
-          <t>20834194****6625799</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2502,20 +2395,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>11499</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+86-135****9925</t>
+        </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>+86-135****9925</t>
+          <t>2083378868570218500</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
-        <is>
-          <t>2083378868570218500</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2562,20 +2452,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>149</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>+86-158****6671</t>
+        </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>+86-158****6671</t>
+          <t>208345132****212679</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
-        <is>
-          <t>208345132****212679</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2622,20 +2509,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>9797</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>+86-185****8868</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>+86-185****8868</t>
+          <t>2083393526554419209</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
-        <is>
-          <t>2083393526554419209</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2682,20 +2566,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>139</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+86-182****9334</t>
+        </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>+86-182****9334</t>
+          <t>2083438481639473158</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
-        <is>
-          <t>2083438481639473158</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2742,20 +2623,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>9097</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>+86-137****3437</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>+86-137****3437</t>
+          <t>20835186****4193281</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
-        <is>
-          <t>20835186****4193281</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2802,20 +2680,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>598</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+86-176****6676</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>+86-176****6676</t>
+          <t>2083488925279584260</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
-        <is>
-          <t>2083488925279584260</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2862,20 +2737,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>598</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+86-176****6676</t>
+        </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>+86-176****6676</t>
+          <t>2083489110968659969</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
-        <is>
-          <t>2083489110968659969</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2922,20 +2794,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>299</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>157****5096</t>
+        </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>157****5096</t>
+          <t>20835184****5394950</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
-        <is>
-          <t>20835184****5394950</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2982,20 +2851,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>1298</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>+86-137****4592</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>+86-137****4592</t>
+          <t>2083468249950625799</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
-        <is>
-          <t>2083468249950625799</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3042,20 +2908,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>10597</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>+86-137****5157</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>+86-137****5157</t>
+          <t>2083459403900444673</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
-        <is>
-          <t>2083459403900444673</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3102,20 +2965,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>9597</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>+86-185****6381</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>+86-185****6381</t>
+          <t>2083492041394888704</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
-        <is>
-          <t>2083492041394888704</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3162,20 +3022,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>149</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>+86-189****6101</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>+86-189****6101</t>
+          <t>2083535221353807878</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
-        <is>
-          <t>2083535221353807878</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3222,20 +3079,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>149</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+86-136****1011</t>
+        </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>+86-136****1011</t>
+          <t>2083473729850638338</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
-        <is>
-          <t>2083473729850638338</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3282,20 +3136,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>268</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+86-139****5572</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>+86-139****5572</t>
+          <t>2083466044125376518</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
-        <is>
-          <t>2083466044125376518</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3342,20 +3193,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>1298</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>+86-138****9496</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>+86-138****9496</t>
+          <t>20834627171****4854</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
-        <is>
-          <t>20834627171****4854</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3402,20 +3250,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>2196</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+86-136****7692</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>+86-136****7692</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3462,20 +3307,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>798</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+86-136****7692</t>
+        </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>+86-136****7692</t>
+          <t>2083869093608218625</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
-        <is>
-          <t>2083869093608218625</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3522,20 +3364,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>13096</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+86-139****3343</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>+86-139****3343</t>
+          <t>20838158****0227969</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
-        <is>
-          <t>20838158****0227969</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3582,20 +3421,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>1197</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+86-134****3653</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>+86-134****3653</t>
+          <t>2083862067750772743</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
-        <is>
-          <t>2083862067750772743</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3642,20 +3478,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>9997.1</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>+86-138****0953</t>
+        </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>+86-138****0953</t>
+          <t>2083867893785956356</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
-        <is>
-          <t>2083867893785956356</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3702,20 +3535,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>10717.19</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+86-139****1898</t>
+        </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>+86-139****1898</t>
+          <t>2083866761469034502</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
-        <is>
-          <t>2083866761469034502</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3762,20 +3592,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>149</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+86-151****6728</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>+86-151****6728</t>
+          <t>2083827033647800321</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
-        <is>
-          <t>2083827033647800321</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3822,20 +3649,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>1099</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>+86-153****6593</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>+86-153****6593</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3882,20 +3706,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>10708.96</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+86-133****6806</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>+86-133****6806</t>
+          <t>2083826879054483456</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
-        <is>
-          <t>2083826879054483456</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3942,20 +3763,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>1797</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+86-133****6806</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>+86-133****6806</t>
+          <t>2083829974604701703</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
-        <is>
-          <t>2083829974604701703</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4002,20 +3820,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>12597</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>+86-186****0160</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>+86-186****0160</t>
+          <t>2083784830620794886</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
-        <is>
-          <t>2083784830620794886</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4062,20 +3877,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>9499</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>+86-186****3020</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>+86-186****3020</t>
+          <t>2083843530738790407</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
-        <is>
-          <t>2083843530738790407</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4122,20 +3934,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>1499</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>131****2129</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>131****2129</t>
+          <t>2083903589702107144</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
-        <is>
-          <t>2083903589702107144</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4182,20 +3991,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>12598.1</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>131****0218</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>131****0218</t>
+          <t>2083889439111569410</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
-        <is>
-          <t>2083889439111569410</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4242,20 +4048,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>1298</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>+86-135****1432</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>+86-135****1432</t>
+          <t>2083845611390427142</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
-        <is>
-          <t>2083845611390427142</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4302,20 +4105,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>12597</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>+86-150****3779</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>+86-150****3779</t>
+          <t>20838448191****0534</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
-        <is>
-          <t>20838448191****0534</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4362,20 +4162,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>9997.1</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>+86-132****0974</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>+86-132****0974</t>
+          <t>2083842589323927554</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
-        <is>
-          <t>2083842589323927554</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4422,20 +4219,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>1596</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>+86-185****8209</t>
+        </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>+86-185****8209</t>
+          <t>2083880794776854530</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
-        <is>
-          <t>2083880794776854530</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4482,20 +4276,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>698</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>137****3613</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>137****3613</t>
+          <t>2083796531577610241</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
-        <is>
-          <t>2083796531577610241</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4542,20 +4333,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>9597</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>+86-139****3728</t>
+        </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>+86-139****3728</t>
+          <t>2083746005818204162</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
-        <is>
-          <t>2083746005818204162</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4602,20 +4390,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>11997.1</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>+86-138****9653</t>
+        </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>+86-138****9653</t>
+          <t>2083865579702910982</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
-        <is>
-          <t>2083865579702910982</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4662,20 +4447,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>11499</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+86-185****2293</t>
+        </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>+86-185****2293</t>
+          <t>2083837986196086788</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
-        <is>
-          <t>2083837986196086788</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4722,20 +4504,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>1298</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+86-185****1539</t>
+        </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>+86-185****1539</t>
+          <t>20838526155****1762</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
-        <is>
-          <t>20838526155****1762</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4782,20 +4561,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>1649</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+86-185****3180</t>
+        </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>+86-185****3180</t>
+          <t>20838160****6694656</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
-        <is>
-          <t>20838160****6694656</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4842,20 +4618,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>2300</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>+86-136****7990</t>
+        </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>+86-136****7990</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4902,20 +4675,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>1499</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+86-176****7389</t>
+        </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>+86-176****7389</t>
+          <t>2083805331313393670</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
-        <is>
-          <t>2083805331313393670</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4962,20 +4732,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>9499</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>+86-186****0666</t>
+        </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>+86-186****0666</t>
+          <t>2083776290631974912</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
-        <is>
-          <t>2083776290631974912</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5022,20 +4789,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>399</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>2084201196****13991</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
-        <is>
-          <t>2084201196****13991</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5082,20 +4846,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>399</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>2084147****63665921</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
-        <is>
-          <t>2084147****63665921</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5142,20 +4903,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>699</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>134****0961</t>
+        </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>134****0961</t>
+          <t>208422192****579527</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
-        <is>
-          <t>208422192****579527</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5202,20 +4960,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>999</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>+86-136****7388</t>
+        </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>+86-136****7388</t>
+          <t>2084190****27176713</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
-        <is>
-          <t>2084190****27176713</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5262,20 +5017,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>1298</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>+86-178****3201</t>
+        </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>+86-178****3201</t>
+          <t>2084152****70605063</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
-        <is>
-          <t>2084152****70605063</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5322,20 +5074,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>897</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>+86-137****1675</t>
+        </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>+86-137****1675</t>
+          <t>2084232492481650697</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
-        <is>
-          <t>2084232492481650697</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5382,20 +5131,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>798</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>+86-139****8193</t>
+        </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>+86-139****8193</t>
+          <t>2084157****42969605</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
-        <is>
-          <t>2084157****42969605</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5442,20 +5188,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>399</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>+86-136****0631</t>
+        </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>+86-136****0631</t>
+          <t>2084187****44460808</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
-        <is>
-          <t>2084187****44460808</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5502,20 +5245,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>10597</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>+86-196****1061</t>
+        </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>+86-196****1061</t>
+          <t>2084252509638729731</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
-        <is>
-          <t>2084252509638729731</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5562,20 +5302,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>12597</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>+86-136****5703</t>
+        </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>+86-136****5703</t>
+          <t>2084192****75429636</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
-        <is>
-          <t>2084192****75429636</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5622,20 +5359,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>1499</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>+86-185****5271</t>
+        </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>+86-185****5271</t>
+          <t>2083508592578330630</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
-        <is>
-          <t>2083508592578330630</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5682,20 +5416,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>5999</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>+86-158****2008</t>
+        </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>+86-158****2008</t>
+          <t>2084194****66958086</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
-        <is>
-          <t>2084194****66958086</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5742,20 +5473,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>598</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>+86-136****9757</t>
+        </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>+86-136****9757</t>
+          <t>2084255436819595267</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
-        <is>
-          <t>2084255436819595267</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5802,20 +5530,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>9299</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>+86-135****0613</t>
+        </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>+86-135****0613</t>
+          <t>2084222032561561600</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
-        <is>
-          <t>2084222032561561600</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5862,20 +5587,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>2598</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>+86-135****0861</t>
+        </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>+86-135****0861</t>
+          <t>2084178****98749443</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
-        <is>
-          <t>2084178****98749443</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5922,20 +5644,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>10299</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>+86-158****3837</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>+86-158****3837</t>
+          <t>2084480634701414408</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
-        <is>
-          <t>2084480634701414408</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5982,20 +5701,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>11597</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>139****2395</t>
+        </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>139****2395</t>
+          <t>2084584776910643202</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
-        <is>
-          <t>2084584776910643202</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6042,20 +5758,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>1399</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>+86-187****2618</t>
+        </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>+86-187****2618</t>
+          <t>2084577203302047747</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
-        <is>
-          <t>2084577203302047747</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6102,20 +5815,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>9597</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>131****3818</t>
+        </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>131****3818</t>
+          <t>2084582420416565255</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
-        <is>
-          <t>2084582420416565255</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6162,20 +5872,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>12597</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>+86-139****8525</t>
+        </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>+86-139****8525</t>
+          <t>2084563295659663364</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
-        <is>
-          <t>2084563295659663364</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6222,20 +5929,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>12597</v>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>+86-182****5723</t>
+        </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>+86-182****5723</t>
+          <t>2084556561731788801</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
-        <is>
-          <t>2084556561731788801</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6282,20 +5986,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>10717.19</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>+86-159****1014</t>
+        </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>+86-159****1014</t>
+          <t>2084578829391523842</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
-        <is>
-          <t>2084578829391523842</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6342,20 +6043,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>798</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>166****7206</t>
+        </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>166****7206</t>
+          <t>208491136****602752</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
-        <is>
-          <t>208491136****602752</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6402,20 +6100,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>21598</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>181****9239</t>
+        </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>181****9239</t>
+          <t>2084600368103059462</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
-        <is>
-          <t>2084600368103059462</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6462,20 +6157,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>1298</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>+86-133****2199</t>
+        </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>+86-133****2199</t>
+          <t>20849153****8691337</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
-        <is>
-          <t>20849153****8691337</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6522,20 +6214,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>368</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>+86-184****8888</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>+86-184****8888</t>
+          <t>20849152****7220613</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
-        <is>
-          <t>20849152****7220613</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6582,20 +6271,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>1378</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>+86-186****4657</t>
+        </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>+86-186****4657</t>
+          <t>2084894536964186120</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
-        <is>
-          <t>2084894536964186120</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6642,20 +6328,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>11299</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>+86-137****9681</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>+86-137****9681</t>
+          <t>2084829482505408520</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
-        <is>
-          <t>2084829482505408520</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6702,20 +6385,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>798</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>135****4525</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>135****4525</t>
+          <t>2084871296859967489</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
-        <is>
-          <t>2084871296859967489</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6762,20 +6442,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>1399</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>139****8322</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>139****8322</t>
+          <t>20849195****6447749</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
-        <is>
-          <t>20849195****6447749</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6822,20 +6499,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>10097</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>+86-183****7567</t>
+        </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>+86-183****7567</t>
+          <t>2084924210010554374</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
-        <is>
-          <t>2084924210010554374</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6882,20 +6556,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>12595</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>+86-137****7668</t>
+        </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>+86-137****7668</t>
+          <t>20849165****9137415</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
-        <is>
-          <t>20849165****9137415</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6942,20 +6613,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>9299</v>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>+86-187****2384</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>+86-187****2384</t>
+          <t>2084998687974752260</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
-        <is>
-          <t>2084998687974752260</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7002,20 +6670,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>498</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>+86-182****6555</t>
+        </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>+86-182****6555</t>
+          <t>2084975273100976130</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
-        <is>
-          <t>2084975273100976130</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7062,20 +6727,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>298</v>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>+86-139****1165</t>
+        </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>+86-139****1165</t>
+          <t>2084974748826144775</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
-        <is>
-          <t>2084974748826144775</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7122,20 +6784,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>649</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>+86-151****4504</t>
+        </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>+86-151****4504</t>
+          <t>2084883374583341065</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
-        <is>
-          <t>2084883374583341065</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7182,20 +6841,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>498</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>+86-150****7892</t>
+        </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>+86-150****7892</t>
+          <t>2084852832236150789</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
-        <is>
-          <t>2084852832236150789</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7242,20 +6898,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>66</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>+86-139****2518</t>
+        </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>+86-139****2518</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7302,20 +6955,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>14500</v>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>+86-186****1534</t>
+        </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>+86-186****1534</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7362,20 +7012,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>13799</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>+86-158****6261</t>
+        </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>+86-158****6261</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7422,20 +7069,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>199</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>+86-186****9666</t>
+        </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>+86-186****9666</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7482,20 +7126,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>100</v>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>+86-138****2964</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>+86-138****2964</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7542,20 +7183,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>200</v>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>+86-137****5245</t>
+        </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>+86-137****5245</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7602,20 +7240,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>11999</v>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>+86-133****6607</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>+86-133****6607</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7662,20 +7297,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>4479</v>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>+86-158****9578</t>
+        </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>+86-158****9578</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7722,20 +7354,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>199</v>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7782,20 +7411,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>10499</v>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>+86-190****1802</t>
+        </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>+86-190****1802</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7842,20 +7468,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>19999</v>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>+86-156****1888</t>
+        </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>+86-156****1888</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7902,20 +7525,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>579</v>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>+86-136****0769</t>
+        </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>+86-136****0769</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7962,20 +7582,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>15496</v>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8022,20 +7639,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>12999</v>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8082,20 +7696,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>11499</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>+86-186****7992</t>
+        </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>+86-186****7992</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8142,20 +7753,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>8508</v>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>135****5178</t>
+        </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>135****5178</t>
+          <t>260801000210361243</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
-        <is>
-          <t>260801000210361243</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -8202,20 +7810,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>8508</v>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>135****5178</t>
+        </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>135****5178</t>
+          <t>260801000210359210</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
-        <is>
-          <t>260801000210359210</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -8262,20 +7867,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>7499</v>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>158****6735</t>
+        </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>158****6735</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8322,20 +7924,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>3</v>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>185****8918</t>
+        </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>185****8918</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8382,20 +7981,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>11500</v>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>185****8918</t>
+        </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>185****8918</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8442,20 +8038,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I134" t="n">
-        <v>100</v>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>+86-139****8563</t>
+        </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>+86-139****8563</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8502,20 +8095,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>1199</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>+86-186****3681</t>
+        </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>+86-186****3681</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8562,20 +8152,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I136" t="n">
-        <v>11999</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>+86-132****5290</t>
+        </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>+86-132****5290</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8622,20 +8209,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>14999</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>+86-189****0781</t>
+        </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>+86-189****0781</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8682,20 +8266,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>12999</v>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>+86-137****4764</t>
+        </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>+86-137****4764</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8742,20 +8323,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>1319</v>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>+86-173****8086</t>
+        </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>+86-173****8086</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8802,20 +8380,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>200</v>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>+86-133****8655</t>
+        </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>+86-133****8655</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8862,20 +8437,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>200</v>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>+86-133****3358</t>
+        </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>+86-133****3358</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -8922,20 +8494,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>199</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>+86-137****3871</t>
+        </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>+86-137****3871</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8982,20 +8551,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>1199</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>+86-135****2380</t>
+        </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>+86-135****2380</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9042,20 +8608,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>69</v>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>+86-187****1204</t>
+        </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>+86-187****1204</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9102,20 +8665,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>13999</v>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>+86-158****7802</t>
+        </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>+86-158****7802</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9162,20 +8722,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>1249</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>+86-137****5188</t>
+        </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>+86-137****5188</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9222,20 +8779,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>4498</v>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>+86-156****9614</t>
+        </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>+86-156****9614</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9282,20 +8836,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>9196</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9342,20 +8893,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>6999</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9402,20 +8950,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>16497</v>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9462,20 +9007,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I151" t="n">
-        <v>12699</v>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>+86-139****3939</t>
+        </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>+86-139****3939</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9522,20 +9064,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>12500</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>+86-132****9058</t>
+        </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>+86-132****9058</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9582,20 +9121,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I153" t="n">
-        <v>300</v>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>+86-185****8357</t>
+        </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>+86-185****8357</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9642,20 +9178,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I154" t="n">
-        <v>50</v>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>+86-151****4775</t>
+        </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>+86-151****4775</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9702,20 +9235,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I155" t="n">
-        <v>599</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>+86-131****8359</t>
+        </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9762,20 +9292,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I156" t="n">
-        <v>599</v>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>+86-131****8359</t>
+        </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -9822,20 +9349,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I157" t="n">
-        <v>12599</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>+86-131****8359</t>
+        </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9882,20 +9406,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>199</v>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>+86-131****8359</t>
+        </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -9942,20 +9463,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I159" t="n">
-        <v>49</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>139****9854</t>
+        </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>139****9854</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10002,20 +9520,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I160" t="n">
-        <v>8299</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>+86-158****7802</t>
+        </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>+86-158****7802</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10062,20 +9577,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I161" t="n">
-        <v>13800</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>+86-188****0892</t>
+        </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>+86-188****0892</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10122,20 +9634,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I162" t="n">
-        <v>10</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>+86-136****3866</t>
+        </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>+86-136****3866</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10182,20 +9691,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I163" t="n">
-        <v>5197</v>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>+86-186****2999</t>
+        </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>+86-186****2999</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10242,20 +9748,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I164" t="n">
-        <v>99</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>+86-136****4596</t>
+        </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>+86-136****4596</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10302,20 +9805,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>200</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>+86-135****3541</t>
+        </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>+86-135****3541</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10362,20 +9862,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I166" t="n">
-        <v>85</v>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>+86-136****6230</t>
+        </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>+86-136****6230</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10422,20 +9919,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I167" t="n">
-        <v>1000</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>+86-135****7391</t>
+        </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>+86-135****7391</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10482,20 +9976,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I168" t="n">
-        <v>6899</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>+86-187****9725</t>
+        </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>+86-187****9725</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10542,20 +10033,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>99</v>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>+86-136****2871</t>
+        </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>+86-136****2871</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10602,20 +10090,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I170" t="n">
-        <v>99</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>+86-136****4417</t>
+        </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>+86-136****4417</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -10662,20 +10147,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I171" t="n">
-        <v>299</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>+86-139****6913</t>
+        </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>+86-139****6913</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10722,20 +10204,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I172" t="n">
-        <v>100</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>+86-136****5348</t>
+        </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>+86-136****5348</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10782,20 +10261,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I173" t="n">
-        <v>1149</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>+86-135****7766</t>
+        </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>+86-135****7766</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10842,20 +10318,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>1</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>+86-178****1967</t>
+        </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>+86-178****1967</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10902,20 +10375,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I175" t="n">
-        <v>0.1</v>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>153****1994</t>
+        </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>153****1994</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10962,20 +10432,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I176" t="n">
-        <v>3799</v>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>+86-156****9614</t>
+        </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>+86-156****9614</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11022,20 +10489,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I177" t="n">
-        <v>4597</v>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>+86-151****0897</t>
+        </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>+86-151****0897</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -11082,20 +10546,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I178" t="n">
-        <v>200</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>+86-185****1770</t>
+        </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>+86-185****1770</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11142,20 +10603,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>10299</v>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>+86-187****8972</t>
+        </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>+86-187****8972</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11202,20 +10660,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>498</v>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>+86-158****1870</t>
+        </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>+86-158****1870</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11262,20 +10717,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>194</v>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>188****2372</t>
+        </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>188****2372</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -11322,20 +10774,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>500</v>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>133****0100</t>
+        </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>133****0100</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11382,20 +10831,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I183" t="n">
-        <v>0.4</v>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>133****0100</t>
+        </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>133****0100</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11442,20 +10888,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>200</v>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>+86-198****6299</t>
+        </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>+86-198****6299</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11502,20 +10945,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>500</v>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>+86-198****6299</t>
+        </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>+86-198****6299</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11562,20 +11002,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I186" t="n">
-        <v>22497</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>+86-152****5172</t>
+        </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>+86-152****5172</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11622,20 +11059,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I187" t="n">
-        <v>19299</v>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>+86-152****5512</t>
+        </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>+86-152****5512</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11682,20 +11116,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I188" t="n">
-        <v>4201</v>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>+86-176****1972</t>
+        </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>+86-176****1972</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -11742,20 +11173,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I189" t="n">
-        <v>1899</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>189****0307</t>
+        </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>189****0307</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11802,20 +11230,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I190" t="n">
-        <v>8299</v>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>182****4561</t>
+        </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>182****4561</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11862,20 +11287,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>778</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>+86-185****1711</t>
+        </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>+86-185****1711</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11922,20 +11344,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I192" t="n">
-        <v>12799</v>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>+86-133****4816</t>
+        </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>+86-133****4816</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -11982,20 +11401,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>11699</v>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>+86-132****0312</t>
+        </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>+86-132****0312</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12042,20 +11458,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I194" t="n">
-        <v>7299</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>139****5407</t>
+        </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>139****5407</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12102,20 +11515,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>1999</v>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>+86-186****2128</t>
+        </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>+86-186****2128</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12162,20 +11572,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I196" t="n">
-        <v>2999</v>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12222,20 +11629,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I197" t="n">
-        <v>4026</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12282,20 +11686,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I198" t="n">
-        <v>599</v>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12342,20 +11743,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I199" t="n">
-        <v>3917</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>177****2965</t>
+        </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>177****2965</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12402,20 +11800,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I200" t="n">
-        <v>1398</v>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>184****5224</t>
+        </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>184****5224</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12462,20 +11857,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I201" t="n">
-        <v>3697</v>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12522,20 +11914,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I202" t="n">
-        <v>5999</v>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12582,20 +11971,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I203" t="n">
-        <v>2767</v>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>137****2423</t>
+        </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>137****2423</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12642,20 +12028,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I204" t="n">
-        <v>3799</v>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12702,20 +12085,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I205" t="n">
-        <v>3218</v>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12762,20 +12142,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I206" t="n">
-        <v>3355</v>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>135****5980</t>
+        </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12822,20 +12199,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I207" t="n">
-        <v>2298</v>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>135****5980</t>
+        </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12882,20 +12256,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I208" t="n">
-        <v>5499</v>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>158****9456</t>
+        </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>158****9456</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L208" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12942,20 +12313,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I209" t="n">
-        <v>558</v>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>+86-183****7721</t>
+        </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>+86-183****7721</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13002,20 +12370,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I210" t="n">
-        <v>1698</v>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13062,20 +12427,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I211" t="n">
-        <v>4174</v>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13122,20 +12484,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I212" t="n">
-        <v>3799</v>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13182,20 +12541,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I213" t="n">
-        <v>3799</v>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13242,20 +12598,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I214" t="n">
-        <v>3898</v>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>172****4364</t>
+        </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>172****4364</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13302,20 +12655,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I215" t="n">
-        <v>5244</v>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>138****7017</t>
+        </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>138****7017</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13362,20 +12712,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I216" t="n">
-        <v>5845</v>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>135****5980</t>
+        </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13422,20 +12769,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I217" t="n">
-        <v>699</v>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13482,20 +12826,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I218" t="n">
-        <v>4299</v>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>138****1500</t>
+        </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>138****1500</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13542,20 +12883,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I219" t="n">
-        <v>3108</v>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>157****2651</t>
+        </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>157****2651</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13602,20 +12940,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I220" t="n">
-        <v>3799</v>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>134****2963</t>
+        </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>134****2963</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13662,20 +12997,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I221" t="n">
-        <v>23655</v>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>186****1441</t>
+        </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>186****1441</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13722,20 +13054,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I222" t="n">
-        <v>3799</v>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>186****9390</t>
+        </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>186****9390</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13782,20 +13111,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I223" t="n">
-        <v>4334</v>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>152****3830</t>
+        </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>152****3830</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13842,20 +13168,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I224" t="n">
-        <v>1299</v>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L224" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13902,20 +13225,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I225" t="n">
-        <v>3646</v>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>173****2982</t>
+        </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>173****2982</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13962,20 +13282,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I226" t="n">
-        <v>5999</v>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>135****2633</t>
+        </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>135****2633</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14022,20 +13339,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I227" t="n">
-        <v>4148</v>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>151****7380</t>
+        </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>151****7380</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14082,20 +13396,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I228" t="n">
-        <v>159</v>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>134****3737</t>
+        </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>134****3737</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14142,20 +13453,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I229" t="n">
-        <v>3827</v>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14202,20 +13510,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I230" t="n">
-        <v>198</v>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>+86-181****3714</t>
+        </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>+86-181****3714</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14262,20 +13567,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I231" t="n">
-        <v>280</v>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>+86-134****6425</t>
+        </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>+86-134****6425</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14322,20 +13624,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I232" t="n">
-        <v>198</v>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>+86-186****1921</t>
+        </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>+86-186****1921</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14382,20 +13681,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I233" t="n">
-        <v>100</v>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>+86-159****4633</t>
+        </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>+86-159****4633</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14442,20 +13738,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I234" t="n">
-        <v>2699</v>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>+86-136****8289</t>
+        </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>+86-136****8289</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14502,20 +13795,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I235" t="n">
-        <v>178</v>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>139****7878</t>
+        </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>139****7878</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14562,20 +13852,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I236" t="n">
-        <v>178</v>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>139****0299</t>
+        </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>139****0299</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L236" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14622,20 +13909,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I237" t="n">
-        <v>280</v>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>159****9395</t>
+        </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>159****9395</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14682,20 +13966,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I238" t="n">
-        <v>79</v>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>+86-178****0594</t>
+        </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>+86-178****0594</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14742,20 +14023,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I239" t="n">
-        <v>7499</v>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>+86-189****0178</t>
+        </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>+86-189****0178</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14802,20 +14080,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I240" t="n">
-        <v>799</v>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>+86-130****1120</t>
+        </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>+86-130****1120</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L240" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
